--- a/excel/Restaurant-Solution.xlsx
+++ b/excel/Restaurant-Solution.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boyko\stats\opt2025\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Boyko Amarov\stats\opt2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA4FAA3-99C3-46C4-AF6A-7F3CB5796A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4812" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{1A8FE5F9-102C-49B6-9C1B-35C31C178295}"/>
+    <workbookView xWindow="27000" yWindow="4695" windowWidth="22725" windowHeight="11760" xr2:uid="{1A8FE5F9-102C-49B6-9C1B-35C31C178295}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
@@ -522,13 +522,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A61F620-D7AE-45E3-AD2D-3824A403C130}">
   <dimension ref="B2:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -548,7 +548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -569,7 +569,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -590,7 +590,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -611,7 +611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -649,7 +649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
@@ -663,7 +663,7 @@
         <v>3.333333333333333</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C9" s="1">
         <v>0</v>
       </c>
@@ -674,7 +674,7 @@
         <v>3.0000000000000004</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C10" s="1">
         <v>0</v>
       </c>
@@ -685,7 +685,7 @@
         <v>3.1250000000000009</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>12</v>
       </c>

--- a/excel/Restaurant-Solution.xlsx
+++ b/excel/Restaurant-Solution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Boyko Amarov\stats\opt2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA4FAA3-99C3-46C4-AF6A-7F3CB5796A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D697D24-24E6-4D9F-8B14-80B1AA7A21EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27000" yWindow="4695" windowWidth="22725" windowHeight="11760" xr2:uid="{1A8FE5F9-102C-49B6-9C1B-35C31C178295}"/>
   </bookViews>
@@ -525,7 +525,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
